--- a/VerveStacks_FRA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC51DAAF-57ED-4A42-AB32-688A2C1FF20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FDEF5F-9B06-41FC-B481-03421773A6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6153,7 +6153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01304E24-4493-4931-83BF-E43D6C3FE00F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{606D36A0-83B4-4D4F-82D9-7A9BFD3D3322}">
   <dimension ref="B3:H89"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FDEF5F-9B06-41FC-B481-03421773A6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF1A3A2-4352-415F-BCA9-BFE7A8974E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6153,7 +6153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{606D36A0-83B4-4D4F-82D9-7A9BFD3D3322}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8095BDB5-7AC3-4FE9-88AA-32642A74F7C8}">
   <dimension ref="B3:H89"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF1A3A2-4352-415F-BCA9-BFE7A8974E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B798C334-26C1-42AB-8F1F-C4369E298D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6153,7 +6153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8095BDB5-7AC3-4FE9-88AA-32642A74F7C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E76BC6-626B-4A35-90D8-B7C70B771E97}">
   <dimension ref="B3:H89"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B798C334-26C1-42AB-8F1F-C4369E298D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605E6A0A-4F89-4B98-A96F-FB77C3E1325A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -6153,7 +6153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E76BC6-626B-4A35-90D8-B7C70B771E97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A982F411-03A0-47A7-A04E-C467DC1C8C94}">
   <dimension ref="B3:H89"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
